--- a/data/plejd_trends_monthly.xlsx
+++ b/data/plejd_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>27</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2025,13 +2025,13 @@
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2095,7 +2095,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
         <v>31</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2380,10 +2380,10 @@
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>41</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66">
@@ -2572,7 +2572,7 @@
         <v>25</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>28</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2668,10 +2668,10 @@
         <v>33</v>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>39</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C73" t="n">
         <v>11</v>
@@ -2799,7 +2799,7 @@
         <v>13</v>
       </c>
       <c r="D74" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>43</v>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2860,13 +2860,13 @@
         <v>30</v>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2991,10 +2991,10 @@
         <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>15</v>
       </c>
       <c r="D82" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>50</v>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D83" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84">
@@ -3119,7 +3119,7 @@
         <v>23</v>
       </c>
       <c r="D84" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3145,7 +3145,7 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C85" t="n">
         <v>21</v>
@@ -3154,7 +3154,7 @@
         <v>35</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3177,22 +3177,22 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C86" t="n">
         <v>19</v>
       </c>
       <c r="D86" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3215,10 +3215,10 @@
         <v>19</v>
       </c>
       <c r="D87" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
@@ -3241,16 +3241,16 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C88" t="n">
         <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E88" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>28</v>
       </c>
       <c r="C89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D89" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3311,10 +3311,10 @@
         <v>17</v>
       </c>
       <c r="D90" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3337,13 +3337,13 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C91" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -3375,10 +3375,10 @@
         <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3404,13 +3404,13 @@
         <v>36</v>
       </c>
       <c r="C93" t="n">
+        <v>24</v>
+      </c>
+      <c r="D93" t="n">
         <v>23</v>
       </c>
-      <c r="D93" t="n">
-        <v>32</v>
-      </c>
       <c r="E93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3439,10 +3439,10 @@
         <v>28</v>
       </c>
       <c r="D94" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3468,19 +3468,19 @@
         <v>51</v>
       </c>
       <c r="C95" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96">
@@ -3500,13 +3500,13 @@
         <v>59</v>
       </c>
       <c r="C96" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D96" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E96" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3529,22 +3529,22 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C97" t="n">
         <v>33</v>
       </c>
       <c r="D97" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3561,22 +3561,22 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C98" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E98" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99">
@@ -3596,13 +3596,13 @@
         <v>41</v>
       </c>
       <c r="C99" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D99" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E99" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -3628,19 +3628,19 @@
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E100" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3657,16 +3657,16 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C101" t="n">
         <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E101" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3678,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102">
@@ -3698,7 +3698,7 @@
         <v>30</v>
       </c>
       <c r="E102" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103">
@@ -3727,10 +3727,10 @@
         <v>30</v>
       </c>
       <c r="D103" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E103" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3759,16 +3759,16 @@
         <v>28</v>
       </c>
       <c r="D104" t="n">
+        <v>28</v>
+      </c>
+      <c r="E104" t="n">
+        <v>29</v>
+      </c>
+      <c r="F104" t="n">
+        <v>66</v>
+      </c>
+      <c r="G104" t="n">
         <v>23</v>
-      </c>
-      <c r="E104" t="n">
-        <v>31</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>31</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C105" t="n">
         <v>35</v>
       </c>
       <c r="D105" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E105" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>52</v>
       </c>
       <c r="C106" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D106" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E106" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -3852,19 +3852,19 @@
         <v>65</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D107" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E107" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3884,10 +3884,10 @@
         <v>74</v>
       </c>
       <c r="C108" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D108" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E108" t="n">
         <v>41</v>
@@ -3902,10 +3902,10 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J108" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
@@ -3913,16 +3913,16 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D109" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E109" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3945,22 +3945,22 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C110" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D110" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E110" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3980,25 +3980,25 @@
         <v>52</v>
       </c>
       <c r="C111" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D111" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E111" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -4012,25 +4012,25 @@
         <v>44</v>
       </c>
       <c r="C112" t="n">
+        <v>56</v>
+      </c>
+      <c r="D112" t="n">
         <v>55</v>
       </c>
-      <c r="D112" t="n">
-        <v>56</v>
-      </c>
       <c r="E112" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -4044,19 +4044,19 @@
         <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D113" t="n">
         <v>55</v>
       </c>
       <c r="E113" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -4076,25 +4076,25 @@
         <v>43</v>
       </c>
       <c r="C114" t="n">
+        <v>38</v>
+      </c>
+      <c r="D114" t="n">
+        <v>48</v>
+      </c>
+      <c r="E114" t="n">
+        <v>36</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
         <v>37</v>
       </c>
-      <c r="D114" t="n">
-        <v>42</v>
-      </c>
-      <c r="E114" t="n">
-        <v>44</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>38</v>
-      </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -4108,25 +4108,25 @@
         <v>40</v>
       </c>
       <c r="C115" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D115" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E115" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4137,22 +4137,22 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C116" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D116" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E116" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G116" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -4172,19 +4172,19 @@
         <v>62</v>
       </c>
       <c r="C117" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D117" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E117" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4204,22 +4204,22 @@
         <v>63</v>
       </c>
       <c r="C118" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D118" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E118" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G118" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4233,10 +4233,10 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C119" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D119" t="n">
         <v>100</v>
@@ -4245,16 +4245,16 @@
         <v>65</v>
       </c>
       <c r="F119" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G119" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -4271,25 +4271,25 @@
         <v>100</v>
       </c>
       <c r="D120" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E120" t="n">
+        <v>83</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
         <v>92</v>
       </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>98</v>
-      </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121">
@@ -4297,28 +4297,28 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C121" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D121" t="n">
         <v>75</v>
       </c>
       <c r="E121" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -4332,25 +4332,25 @@
         <v>71</v>
       </c>
       <c r="C122" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D122" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E122" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4364,25 +4364,25 @@
         <v>59</v>
       </c>
       <c r="C123" t="n">
+        <v>75</v>
+      </c>
+      <c r="D123" t="n">
+        <v>52</v>
+      </c>
+      <c r="E123" t="n">
         <v>73</v>
       </c>
-      <c r="D123" t="n">
-        <v>43</v>
-      </c>
-      <c r="E123" t="n">
-        <v>79</v>
-      </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -4396,19 +4396,19 @@
         <v>54</v>
       </c>
       <c r="C124" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D124" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E124" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4428,25 +4428,25 @@
         <v>57</v>
       </c>
       <c r="C125" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D125" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E125" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F125" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G125" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -4460,19 +4460,19 @@
         <v>43</v>
       </c>
       <c r="C126" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D126" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E126" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F126" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4492,19 +4492,19 @@
         <v>41</v>
       </c>
       <c r="C127" t="n">
+        <v>52</v>
+      </c>
+      <c r="D127" t="n">
         <v>51</v>
       </c>
-      <c r="D127" t="n">
-        <v>46</v>
-      </c>
       <c r="E127" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128">
@@ -4527,7 +4527,7 @@
         <v>51</v>
       </c>
       <c r="D128" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4556,28 +4556,28 @@
         <v>60</v>
       </c>
       <c r="C129" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D129" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E129" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F129" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J129" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -4585,31 +4585,63 @@
         <v>46295</v>
       </c>
       <c r="B130" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C130" t="n">
+        <v>84</v>
+      </c>
+      <c r="D130" t="n">
+        <v>90</v>
+      </c>
+      <c r="E130" t="n">
+        <v>83</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>68</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+      <c r="I130" t="n">
+        <v>72</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B131" t="n">
         <v>81</v>
       </c>
-      <c r="D130" t="n">
-        <v>81</v>
-      </c>
-      <c r="E130" t="n">
-        <v>84</v>
-      </c>
-      <c r="F130" t="n">
-        <v>47</v>
-      </c>
-      <c r="G130" t="n">
-        <v>60</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
+      <c r="C131" t="n">
+        <v>89</v>
+      </c>
+      <c r="D131" t="n">
+        <v>92</v>
+      </c>
+      <c r="E131" t="n">
+        <v>94</v>
+      </c>
+      <c r="F131" t="n">
+        <v>52</v>
+      </c>
+      <c r="G131" t="n">
         <v>42</v>
       </c>
-      <c r="J130" t="n">
-        <v>0</v>
+      <c r="H131" t="n">
+        <v>26</v>
+      </c>
+      <c r="I131" t="n">
+        <v>64</v>
+      </c>
+      <c r="J131" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
